--- a/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T07:10:15+00:00</t>
+    <t>2026-01-28T12:36:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}aps-comp-1:For automatically generated APS an attester is not allowed {(author.resolve().ofType(Device).count() != author.count() or attester.count() = 0)}</t>
   </si>
   <si>
     <t>Event</t>
@@ -717,7 +717,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -905,7 +905,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1016,7 +1016,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
+Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
